--- a/cds_files/Houston_CDS_2023-2024.xlsx
+++ b/cds_files/Houston_CDS_2023-2024.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="C3" t="n">
         <v>0.18</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="C4" t="n">
         <v>0.82</v>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.58</v>
+        <v>0.584</v>
       </c>
     </row>
   </sheetData>
